--- a/weather_data.xlsx
+++ b/weather_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -714,6 +714,294 @@
         <v>40.75</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B10" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:54:40</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B11" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:54:53</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B12" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:54:59</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B13" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:56:07</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B14" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:56:13</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B15" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:56:49</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B16" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:58:17</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>45</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B17" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:58:23</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>45</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="B18" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Lisbon</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-04-17 17:58:28</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>45</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1016</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>few clouds</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>20.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
